--- a/backend/artifacts/corrosion.xlsx
+++ b/backend/artifacts/corrosion.xlsx
@@ -474,7 +474,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Corrosion Monitoring  |  Generated: 2026-09-15 06:51 UTC</t>
+          <t>Corrosion Monitoring  |  Generated: 2026-09-15 16:10 UTC</t>
         </is>
       </c>
     </row>

--- a/backend/artifacts/corrosion.xlsx
+++ b/backend/artifacts/corrosion.xlsx
@@ -474,7 +474,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Corrosion Monitoring  |  Generated: 2026-09-15 16:10 UTC</t>
+          <t>Corrosion Monitoring  |  Generated: 2026-09-16 06:25 UTC</t>
         </is>
       </c>
     </row>

--- a/backend/artifacts/corrosion.xlsx
+++ b/backend/artifacts/corrosion.xlsx
@@ -474,7 +474,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Corrosion Monitoring  |  Generated: 2026-09-15 06:51 UTC</t>
+          <t>Corrosion Monitoring  |  Generated: 2026-09-16 16:20 UTC</t>
         </is>
       </c>
     </row>
